--- a/Modules/VU/VU_BOM_THT.xlsx
+++ b/Modules/VU/VU_BOM_THT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My-Dev\Modular Synth\Avalon Harmonics\VU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{723E56D9-B1A8-49FE-B930-814704269A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8258D21-12E2-4B09-9A46-E7131A71C531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -146,15 +146,9 @@
     <t>Pushernut</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/black-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Gold</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/pushernuts-gold-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Jack Nut</t>
   </si>
   <si>
@@ -784,6 +778,12 @@
   </si>
   <si>
     <t>******* Solder the plastic side of the angled header on the J_B side, and the metal on J_A side. Cut off the excess length.</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57164621578504</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57166910816520</t>
   </si>
 </sst>
 </file>
@@ -1768,7 +1768,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="G2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -1803,16 +1803,16 @@
         <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>31</v>
@@ -1826,16 +1826,16 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
         <v>21</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>31</v>
@@ -1849,16 +1849,16 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>31</v>
@@ -1869,19 +1869,19 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
         <v>21</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>31</v>
@@ -1895,16 +1895,16 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
         <v>21</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>31</v>
@@ -1915,13 +1915,13 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
         <v>21</v>
@@ -1930,7 +1930,7 @@
         <v>31</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -1938,22 +1938,22 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1961,22 +1961,22 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -1984,22 +1984,22 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J11" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -2010,19 +2010,19 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -2030,22 +2030,22 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="E13" t="s">
         <v>104</v>
       </c>
-      <c r="D13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" t="s">
-        <v>106</v>
-      </c>
       <c r="F13" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J13" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -2056,19 +2056,19 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J14" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -2082,16 +2082,16 @@
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E15" t="s">
         <v>22</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J15" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -2105,16 +2105,16 @@
         <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E16" t="s">
         <v>23</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -2128,13 +2128,13 @@
         <v>28</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E17" t="s">
         <v>29</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>32</v>
@@ -2148,16 +2148,16 @@
         <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E18" t="s">
         <v>29</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>32</v>
@@ -2168,22 +2168,22 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C19" t="s">
         <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E19" t="s">
         <v>17</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J19" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -2191,22 +2191,22 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J20" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -2226,10 +2226,10 @@
         <v>26</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J21" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -2237,22 +2237,22 @@
         <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J22" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -2260,22 +2260,22 @@
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C23" t="s">
         <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E23" t="s">
         <v>13</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J23" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -2283,22 +2283,22 @@
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C24" t="s">
         <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J24" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -2306,19 +2306,19 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C25" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="E25" t="s">
-        <v>74</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -2326,13 +2326,13 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s">
         <v>33</v>
       </c>
       <c r="D26" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E26" t="s">
         <v>25</v>
@@ -2341,7 +2341,7 @@
         <v>34</v>
       </c>
       <c r="J26" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -2349,22 +2349,22 @@
         <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D27" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E27" t="s">
         <v>24</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J27" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -2372,22 +2372,22 @@
         <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E28" t="s">
         <v>24</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J28" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -2395,10 +2395,10 @@
         <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D29" t="s">
         <v>15</v>
@@ -2407,10 +2407,10 @@
         <v>24</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J29" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -2424,13 +2424,13 @@
         <v>36</v>
       </c>
       <c r="E31" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="J31" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -2438,19 +2438,19 @@
         <v>2</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C32" t="s">
         <v>36</v>
       </c>
       <c r="E32" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="J32" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -2461,16 +2461,16 @@
         <v>35</v>
       </c>
       <c r="C33" t="s">
+        <v>79</v>
+      </c>
+      <c r="E33" t="s">
+        <v>80</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E33" t="s">
-        <v>82</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="J33" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -2481,16 +2481,16 @@
         <v>35</v>
       </c>
       <c r="C34" t="s">
+        <v>86</v>
+      </c>
+      <c r="E34" t="s">
+        <v>87</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E34" t="s">
-        <v>89</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="J34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -2498,7 +2498,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B36" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -2506,57 +2506,57 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B38" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B39" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B40" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B41" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B42" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B43" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B44" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2572,33 +2572,33 @@
     <hyperlink ref="F16" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
     <hyperlink ref="F21" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
     <hyperlink ref="F26" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="F31" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="F32" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="J6" r:id="rId14" xr:uid="{63E498A3-A2A4-4285-9155-1BD341D4DCB5}"/>
-    <hyperlink ref="F8" r:id="rId15" xr:uid="{E7FE330F-8A3B-4669-8B30-2C9E9A5FC581}"/>
-    <hyperlink ref="F11" r:id="rId16" xr:uid="{B28DEF61-CF1F-4F61-AD51-8A23E6AFB24D}"/>
-    <hyperlink ref="J18" r:id="rId17" xr:uid="{69B674E5-918E-4C55-9473-EE3B4A218C54}"/>
-    <hyperlink ref="F19" r:id="rId18" xr:uid="{D29AE626-DF4E-4773-AA8D-0524E4224C52}"/>
-    <hyperlink ref="F20" r:id="rId19" xr:uid="{A59D37D6-A940-423C-9F03-07E51A21CDF8}"/>
-    <hyperlink ref="F22" r:id="rId20" xr:uid="{82E34BDF-736F-4F98-A76A-B89827876B4D}"/>
-    <hyperlink ref="F23" r:id="rId21" xr:uid="{BA0C518E-2948-45FD-9328-DAE3823EA657}"/>
-    <hyperlink ref="F24" r:id="rId22" xr:uid="{ABDD5C1F-0AC0-49FC-B475-2179875D8E55}"/>
-    <hyperlink ref="F25" r:id="rId23" xr:uid="{4B9DD349-A0F7-425B-94BE-B03C8415B82A}"/>
-    <hyperlink ref="F33" r:id="rId24" xr:uid="{4A11A930-DB4E-4E4A-837D-1777192D19A3}"/>
-    <hyperlink ref="F9" r:id="rId25" xr:uid="{8EF245E9-A8EB-4201-BC07-0FBF381FF66F}"/>
-    <hyperlink ref="F10" r:id="rId26" xr:uid="{4AE9100C-997D-4003-B37A-A25D3512342D}"/>
-    <hyperlink ref="F34" r:id="rId27" xr:uid="{908C5348-17D7-474A-8258-C59855842B28}"/>
-    <hyperlink ref="F27" r:id="rId28" xr:uid="{56A73993-B2DB-4837-AFF8-25F5156F7AF0}"/>
-    <hyperlink ref="F28" r:id="rId29" xr:uid="{D08A31B4-39E6-4E55-8548-0981C02FC257}"/>
-    <hyperlink ref="F29" r:id="rId30" xr:uid="{FE8D99FE-F126-4D68-9F66-9C5F628C4A63}"/>
-    <hyperlink ref="F3" r:id="rId31" xr:uid="{F5E86E2A-248F-42F3-AB17-6681142F9BFC}"/>
-    <hyperlink ref="F4" r:id="rId32" xr:uid="{601160EC-ACF9-442F-97A5-481F9E5EB1DC}"/>
-    <hyperlink ref="F5" r:id="rId33" xr:uid="{17B89E03-18C3-462A-8312-8A6F215480AC}"/>
-    <hyperlink ref="F6" r:id="rId34" xr:uid="{661826B7-D085-4149-AD76-217299348812}"/>
-    <hyperlink ref="F7" r:id="rId35" xr:uid="{2AF8AEE3-3F68-4E2A-8F2C-98395C84238C}"/>
-    <hyperlink ref="J8" r:id="rId36" xr:uid="{40B31D5A-B43C-471B-92E7-4981900768AC}"/>
-    <hyperlink ref="F17" r:id="rId37" xr:uid="{E8350254-F63F-4086-A74F-FA772975FD15}"/>
-    <hyperlink ref="F18" r:id="rId38" xr:uid="{FC450F80-CCB0-4694-BF61-DF1D3F2AF604}"/>
+    <hyperlink ref="J6" r:id="rId12" xr:uid="{63E498A3-A2A4-4285-9155-1BD341D4DCB5}"/>
+    <hyperlink ref="F8" r:id="rId13" xr:uid="{E7FE330F-8A3B-4669-8B30-2C9E9A5FC581}"/>
+    <hyperlink ref="F11" r:id="rId14" xr:uid="{B28DEF61-CF1F-4F61-AD51-8A23E6AFB24D}"/>
+    <hyperlink ref="J18" r:id="rId15" xr:uid="{69B674E5-918E-4C55-9473-EE3B4A218C54}"/>
+    <hyperlink ref="F19" r:id="rId16" xr:uid="{D29AE626-DF4E-4773-AA8D-0524E4224C52}"/>
+    <hyperlink ref="F20" r:id="rId17" xr:uid="{A59D37D6-A940-423C-9F03-07E51A21CDF8}"/>
+    <hyperlink ref="F22" r:id="rId18" xr:uid="{82E34BDF-736F-4F98-A76A-B89827876B4D}"/>
+    <hyperlink ref="F23" r:id="rId19" xr:uid="{BA0C518E-2948-45FD-9328-DAE3823EA657}"/>
+    <hyperlink ref="F24" r:id="rId20" xr:uid="{ABDD5C1F-0AC0-49FC-B475-2179875D8E55}"/>
+    <hyperlink ref="F25" r:id="rId21" xr:uid="{4B9DD349-A0F7-425B-94BE-B03C8415B82A}"/>
+    <hyperlink ref="F33" r:id="rId22" xr:uid="{4A11A930-DB4E-4E4A-837D-1777192D19A3}"/>
+    <hyperlink ref="F9" r:id="rId23" xr:uid="{8EF245E9-A8EB-4201-BC07-0FBF381FF66F}"/>
+    <hyperlink ref="F10" r:id="rId24" xr:uid="{4AE9100C-997D-4003-B37A-A25D3512342D}"/>
+    <hyperlink ref="F34" r:id="rId25" xr:uid="{908C5348-17D7-474A-8258-C59855842B28}"/>
+    <hyperlink ref="F27" r:id="rId26" xr:uid="{56A73993-B2DB-4837-AFF8-25F5156F7AF0}"/>
+    <hyperlink ref="F28" r:id="rId27" xr:uid="{D08A31B4-39E6-4E55-8548-0981C02FC257}"/>
+    <hyperlink ref="F29" r:id="rId28" xr:uid="{FE8D99FE-F126-4D68-9F66-9C5F628C4A63}"/>
+    <hyperlink ref="F3" r:id="rId29" xr:uid="{F5E86E2A-248F-42F3-AB17-6681142F9BFC}"/>
+    <hyperlink ref="F4" r:id="rId30" xr:uid="{601160EC-ACF9-442F-97A5-481F9E5EB1DC}"/>
+    <hyperlink ref="F5" r:id="rId31" xr:uid="{17B89E03-18C3-462A-8312-8A6F215480AC}"/>
+    <hyperlink ref="F6" r:id="rId32" xr:uid="{661826B7-D085-4149-AD76-217299348812}"/>
+    <hyperlink ref="F7" r:id="rId33" xr:uid="{2AF8AEE3-3F68-4E2A-8F2C-98395C84238C}"/>
+    <hyperlink ref="J8" r:id="rId34" xr:uid="{40B31D5A-B43C-471B-92E7-4981900768AC}"/>
+    <hyperlink ref="F17" r:id="rId35" xr:uid="{E8350254-F63F-4086-A74F-FA772975FD15}"/>
+    <hyperlink ref="F18" r:id="rId36" xr:uid="{FC450F80-CCB0-4694-BF61-DF1D3F2AF604}"/>
+    <hyperlink ref="F31" r:id="rId37" xr:uid="{82F320E2-0DD6-4832-A445-7E1C6C0B73A3}"/>
+    <hyperlink ref="F32" r:id="rId38" xr:uid="{0CDD4408-2DB2-47B9-AB63-45DAA2D08883}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId39"/>
